--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484252_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484252_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.065</v>
+        <v>8.989800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4015</v>
+        <v>6.6531</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6635</v>
+        <v>2.3367</v>
       </c>
       <c r="G2" t="n">
         <v>4.8175</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4661</v>
+        <v>2.3909</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2122</v>
+        <v>1.4638</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2539</v>
+        <v>0.927</v>
       </c>
       <c r="V2" t="n">
         <v>0.6093</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.791600000000001</v>
+        <v>7.8512</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2402</v>
+        <v>6.8445</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5514</v>
+        <v>1.0067</v>
       </c>
       <c r="G3" t="n">
         <v>3.9982</v>
@@ -688,13 +688,13 @@
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6882</v>
+        <v>2.7478</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5137</v>
+        <v>2.118</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1746</v>
+        <v>0.6299</v>
       </c>
       <c r="V3" t="n">
         <v>1.4959</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.218</v>
+        <v>7.6885</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8946</v>
+        <v>6.5013</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3233</v>
+        <v>1.1871</v>
       </c>
       <c r="G4" t="n">
         <v>4.6259</v>
@@ -766,13 +766,13 @@
         <v>0.7814</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2945</v>
+        <v>0.176</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>-0.0591</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3713</v>
+        <v>0.2351</v>
       </c>
       <c r="V4" t="n">
         <v>2.1052</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3919</v>
+        <v>4.8781</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4475</v>
+        <v>4.852</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0556</v>
+        <v>0.0261</v>
       </c>
       <c r="G5" t="n">
         <v>4.3726</v>
@@ -844,13 +844,13 @@
         <v>0.9767</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6802</v>
+        <v>-0.194</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2888</v>
+        <v>0.1156</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3913</v>
+        <v>-0.3096</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2649</v>
+        <v>3.7322</v>
       </c>
       <c r="E6" t="n">
-        <v>1.972</v>
+        <v>2.1942</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2929</v>
+        <v>1.5381</v>
       </c>
       <c r="G6" t="n">
         <v>0.8043</v>
@@ -922,13 +922,13 @@
         <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>1.242</v>
+        <v>1.7092</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7567</v>
+        <v>0.9789</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4852</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>1.2186</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.353</v>
+        <v>3.0147</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3956</v>
+        <v>3.9211</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0426</v>
+        <v>-0.9064</v>
       </c>
       <c r="G7" t="n">
         <v>2.1626</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3137</v>
+        <v>0.348</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.6082</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3963</v>
+        <v>-0.2601</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2772</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4063</v>
+        <v>2.9914</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7413</v>
+        <v>-0.2651</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1476</v>
+        <v>3.2565</v>
       </c>
       <c r="G8" t="n">
         <v>2.741</v>
@@ -1078,13 +1078,13 @@
         <v>1.3674</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1311</v>
+        <v>1.454</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>0.8104</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5347</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.5545</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09660000000000001</v>
+        <v>-0.0978</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0644</v>
+        <v>0.761</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9678</v>
+        <v>-0.8588</v>
       </c>
       <c r="G9" t="n">
         <v>2.8129</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1469</v>
+        <v>-0.0475</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2504</v>
+        <v>-0.0529</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1035</v>
+        <v>0.0054</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4959</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9164</v>
+        <v>-1.8183</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0932</v>
+        <v>-0.8148</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1768</v>
+        <v>-1.0035</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8048</v>
+        <v>-0.5778</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8245</v>
+        <v>0.1504</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6293</v>
+        <v>-0.7282</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0643</v>
+        <v>-1.2468</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4298</v>
+        <v>0.0205</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.4941</v>
+        <v>-1.2673</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2595</v>
+        <v>0.669</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3948</v>
+        <v>0.13</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1352</v>
+        <v>0.5391</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4744</v>
+        <v>0.1967</v>
       </c>
       <c r="T10" t="n">
-        <v>1.1199</v>
+        <v>0.432</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6455</v>
+        <v>-0.2353</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9605</v>
+        <v>-1.9141</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8753</v>
+        <v>-3.336</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0852</v>
+        <v>1.4219</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5778</v>
+        <v>-1.8048</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1504</v>
+        <v>0.8245</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7282</v>
+        <v>-2.6293</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2468</v>
+        <v>-2.0643</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0205</v>
+        <v>0.4298</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2673</v>
+        <v>-2.4941</v>
       </c>
       <c r="M11" t="n">
-        <v>0.669</v>
+        <v>0.2595</v>
       </c>
       <c r="N11" t="n">
-        <v>0.13</v>
+        <v>0.3948</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5391</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3907</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8771</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0.4004</v>
+      </c>
+      <c r="V11" t="n">
         <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.3907</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.0545</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.3715</v>
-      </c>
-      <c r="U11" t="n">
-        <v>-0.317</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-1.8279</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71039999999999</v>
+        <v>35.31570000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>26.706</v>
+        <v>27.3113</v>
       </c>
       <c r="F12" t="n">
-        <v>8.004300000000001</v>
+        <v>8.0044</v>
       </c>
       <c r="G12" t="n">
         <v>23.9524</v>
@@ -1372,7 +1372,7 @@
         <v>11.4735</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8008000000000001</v>
+        <v>0.8008000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>-3.2397</v>
@@ -1381,7 +1381,7 @@
         <v>4.0405</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001000000000002665</v>
+        <v>0.0001000000000003221</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.7206</v>
@@ -1390,13 +1390,13 @@
         <v>11.7206</v>
       </c>
       <c r="S12" t="n">
-        <v>8.6526</v>
+        <v>9.2578</v>
       </c>
       <c r="T12" t="n">
-        <v>6.686800000000001</v>
+        <v>7.292</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9661</v>
+        <v>1.9659</v>
       </c>
       <c r="V12" t="n">
         <v>2.1053</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2405</v>
+        <v>0.0332</v>
       </c>
       <c r="E13" t="n">
-        <v>3.9862</v>
+        <v>3.4806</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7457</v>
+        <v>-3.4474</v>
       </c>
       <c r="G13" t="n">
         <v>0.2153</v>
@@ -1468,13 +1468,13 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1386</v>
+        <v>-0.3459</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8118</v>
+        <v>0.3063</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9504</v>
+        <v>-0.6522</v>
       </c>
       <c r="V13" t="n">
         <v>0.5545</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.0795</v>
+        <v>-1.8904</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.348</v>
+        <v>1.358</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2685</v>
+        <v>-3.2484</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-3.0319</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3945</v>
+        <v>-0.8872</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.23</v>
+        <v>-2.1447</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5442</v>
+        <v>0.6394</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0895</v>
+        <v>0.7598</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.1204</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0803</v>
+        <v>-3.6712</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.484</v>
+        <v>-1.647</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4037</v>
+        <v>-2.0243</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1078</v>
+        <v>-1.1906</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8491</v>
+        <v>-0.1326</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7413</v>
+        <v>-1.058</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.5507</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2772</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.9643</v>
+        <v>-2.0957</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2569</v>
+        <v>-2.6625</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2212</v>
+        <v>0.5668</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.0319</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8872</v>
+        <v>-0.3945</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.1447</v>
+        <v>-0.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6394</v>
+        <v>-0.5442</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7598</v>
+        <v>0.0895</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.1204</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6712</v>
+        <v>-0.0803</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.647</v>
+        <v>-0.484</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0243</v>
+        <v>0.4037</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.2645</v>
+        <v>0.0915</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2337</v>
+        <v>0.5346</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0308</v>
+        <v>-0.4431</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.3565</v>
+        <v>-2.2683</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-1.0704</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3872</v>
+        <v>-1.1979</v>
       </c>
       <c r="G16" t="n">
         <v>-2.3461</v>
@@ -1702,13 +1702,13 @@
         <v>0.586</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3803</v>
+        <v>0.4684</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2504</v>
+        <v>0.1493</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1298</v>
+        <v>0.3191</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6404</v>
+        <v>-2.656</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3457</v>
+        <v>-0.1434</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2947</v>
+        <v>-2.5126</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6977</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1028</v>
+        <v>-1.1184</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1732</v>
+        <v>0.029</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9296</v>
+        <v>-1.1474</v>
       </c>
       <c r="V17" t="n">
         <v>0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.4802</v>
+        <v>-3.0601</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0547</v>
+        <v>-0.8525</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4255</v>
+        <v>-2.2076</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7877</v>
@@ -1858,13 +1858,13 @@
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8879</v>
+        <v>-1.4678</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1499</v>
+        <v>-0.9477</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.738</v>
+        <v>-0.5201</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7788</v>
+        <v>-4.469</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8163</v>
+        <v>-0.614</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.9626</v>
+        <v>-3.855</v>
       </c>
       <c r="G19" t="n">
         <v>-3.1632</v>
@@ -1936,13 +1936,13 @@
         <v>1.3674</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4323</v>
+        <v>-1.1225</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6574</v>
+        <v>-0.4552</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7749</v>
+        <v>-0.6673</v>
       </c>
       <c r="V19" t="n">
         <v>-1.5507</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.455</v>
+        <v>-5.2466</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3509</v>
+        <v>-0.4847</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1042</v>
+        <v>-4.7618</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1956</v>
+        <v>-3.266</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.2106</v>
+        <v>0.1059</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.985</v>
+        <v>-3.3719</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.5387</v>
+        <v>-0.284</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.6335</v>
+        <v>1.0642</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.3482</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6569</v>
+        <v>-2.982</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.5771</v>
+        <v>-0.9583</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0797</v>
+        <v>-2.0237</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8808</v>
+        <v>-0.348</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0894</v>
+        <v>-0.2008</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7914</v>
+        <v>-0.1472</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6238</v>
+        <v>-5.4162</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8892</v>
+        <v>-2.1486</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.7346</v>
+        <v>-3.2676</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.266</v>
+        <v>-4.1956</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1059</v>
+        <v>-3.2106</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.3719</v>
+        <v>-0.985</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.284</v>
+        <v>-1.5387</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0642</v>
+        <v>-1.6335</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3482</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.982</v>
+        <v>-2.6569</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9583</v>
+        <v>-1.5771</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0237</v>
+        <v>-1.0797</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7252</v>
+        <v>-1.842</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6052</v>
+        <v>-0.8872</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.12</v>
+        <v>-0.9548</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8279</v>
+        <v>-0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.5724</v>
+        <v>-6.9671</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4733</v>
+        <v>-4.8666</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0991</v>
+        <v>-2.1004</v>
       </c>
       <c r="G22" t="n">
         <v>-4.0554</v>
@@ -2170,13 +2170,13 @@
         <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7086</v>
+        <v>-1.1033</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9684</v>
+        <v>-0.3617</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7403</v>
+        <v>-0.7416</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8317</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-34.7104</v>
+        <v>-34.0362</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.004300000000001</v>
+        <v>-8.004100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-26.7063</v>
+        <v>-26.0319</v>
       </c>
       <c r="G23" t="n">
         <v>-23.9528</v>
@@ -2221,7 +2221,7 @@
         <v>-15.5142</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8008</v>
+        <v>-0.8008000000000002</v>
       </c>
       <c r="K23" t="n">
         <v>3.2398</v>
@@ -2239,7 +2239,7 @@
         <v>-11.4735</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.0001000000000001</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="Q23" t="n">
         <v>-11.7204</v>
@@ -2248,13 +2248,13 @@
         <v>11.7205</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.6526</v>
+        <v>-7.978599999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.9659</v>
+        <v>-1.966</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.6869</v>
+        <v>-6.0126</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1051</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484252_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484252_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.7322</v>
+        <v>3.0147</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1942</v>
+        <v>3.9211</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5381</v>
+        <v>-0.9064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8043</v>
+        <v>2.1626</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6825</v>
+        <v>0.5838</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1218</v>
+        <v>1.5788</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1687</v>
+        <v>3.071</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0463</v>
+        <v>1.7613</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1224</v>
+        <v>1.3097</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3643</v>
+        <v>-0.9085</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3638</v>
+        <v>-1.1775</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.269</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7814</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7092</v>
+        <v>0.348</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9789</v>
+        <v>0.6082</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7302999999999999</v>
+        <v>-0.2601</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2186</v>
+        <v>-0.2772</v>
       </c>
       <c r="W6" t="n">
         <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0147</v>
+        <v>2.9914</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9211</v>
+        <v>-0.2651</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9064</v>
+        <v>3.2565</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1626</v>
+        <v>2.741</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5838</v>
+        <v>1.0016</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5788</v>
+        <v>1.7394</v>
       </c>
       <c r="J7" t="n">
-        <v>3.071</v>
+        <v>1.8824</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7613</v>
+        <v>0.4119</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3097</v>
+        <v>1.4706</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9085</v>
+        <v>0.8585</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1775</v>
+        <v>0.5897</v>
       </c>
       <c r="O7" t="n">
-        <v>0.269</v>
+        <v>0.2688</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-3.1255</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>0.348</v>
+        <v>1.454</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6082</v>
+        <v>0.8104</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2601</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0.5545</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4959</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.9914</v>
+        <v>2.8182</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2651</v>
+        <v>1.2802</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2565</v>
+        <v>1.5381</v>
       </c>
       <c r="G8" t="n">
-        <v>2.741</v>
+        <v>-0.1096</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0016</v>
+        <v>0.3756</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7394</v>
+        <v>-0.4852</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8824</v>
+        <v>0.2547</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4119</v>
+        <v>0.7393</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4706</v>
+        <v>-0.4846</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8585</v>
+        <v>-0.3643</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5897</v>
+        <v>-0.3638</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2688</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7581</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>1.454</v>
+        <v>1.7092</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8104</v>
+        <v>0.9789</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6435999999999999</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5545</v>
+        <v>1.2186</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1675</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0978</v>
+        <v>0.914</v>
       </c>
       <c r="E9" t="n">
-        <v>0.761</v>
+        <v>0.914</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8588</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8129</v>
+        <v>0.914</v>
       </c>
       <c r="H9" t="n">
-        <v>0.372</v>
+        <v>0.307</v>
       </c>
       <c r="I9" t="n">
-        <v>2.441</v>
+        <v>0.607</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7674</v>
+        <v>0.914</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2701</v>
+        <v>0.307</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4972</v>
+        <v>0.607</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0456</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8982</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9437</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0475</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0529</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0054</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. TALTAVULL BALLE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8183</v>
+        <v>-0.0978</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8148</v>
+        <v>0.761</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0035</v>
+        <v>-0.8588</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5778</v>
+        <v>2.8129</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1504</v>
+        <v>0.372</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7282</v>
+        <v>2.441</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2468</v>
+        <v>2.7674</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0205</v>
+        <v>1.2701</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2673</v>
+        <v>1.4972</v>
       </c>
       <c r="M10" t="n">
-        <v>0.669</v>
+        <v>0.0456</v>
       </c>
       <c r="N10" t="n">
-        <v>0.13</v>
+        <v>-0.8982</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5391</v>
+        <v>0.9437</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1967</v>
+        <v>-0.0475</v>
       </c>
       <c r="T10" t="n">
-        <v>0.432</v>
+        <v>-0.0529</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2353</v>
+        <v>0.0054</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. TALTAVULL BALLE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9141</v>
+        <v>-1.8183</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.336</v>
+        <v>-0.8148</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4219</v>
+        <v>-1.0035</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8048</v>
+        <v>-0.5778</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8245</v>
+        <v>0.1504</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6293</v>
+        <v>-0.7282</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0643</v>
+        <v>-1.2468</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4298</v>
+        <v>0.0205</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4941</v>
+        <v>-1.2673</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2595</v>
+        <v>0.669</v>
       </c>
       <c r="N11" t="n">
-        <v>0.3948</v>
+        <v>0.13</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1352</v>
+        <v>0.5391</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4767</v>
+        <v>0.1967</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8771</v>
+        <v>0.432</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4004</v>
+        <v>-0.2353</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>35.31570000000001</v>
+        <v>-1.9141</v>
       </c>
       <c r="E12" t="n">
-        <v>27.3113</v>
+        <v>-3.336</v>
       </c>
       <c r="F12" t="n">
-        <v>8.0044</v>
+        <v>1.4219</v>
       </c>
       <c r="G12" t="n">
-        <v>23.9524</v>
+        <v>-1.8048</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4383</v>
+        <v>0.8245</v>
       </c>
       <c r="I12" t="n">
-        <v>15.5143</v>
+        <v>-2.6293</v>
       </c>
       <c r="J12" t="n">
-        <v>23.1517</v>
+        <v>-2.0643</v>
       </c>
       <c r="K12" t="n">
-        <v>11.6782</v>
+        <v>0.4298</v>
       </c>
       <c r="L12" t="n">
-        <v>11.4735</v>
+        <v>-2.4941</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8008000000000002</v>
+        <v>0.2595</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.2397</v>
+        <v>0.3948</v>
       </c>
       <c r="O12" t="n">
-        <v>4.0405</v>
+        <v>-0.1352</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0001000000000003221</v>
+        <v>-0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.7206</v>
+        <v>-2.1488</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7206</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>9.2578</v>
+        <v>0.4767</v>
       </c>
       <c r="T12" t="n">
-        <v>7.292</v>
+        <v>0.8771</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9659</v>
+        <v>-0.4004</v>
       </c>
       <c r="V12" t="n">
-        <v>2.1053</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>8.588099999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-6.4831</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CB QUART GRUES CRUZ</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0332</v>
+        <v>35.31570000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4806</v>
+        <v>27.3113</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.4474</v>
+        <v>8.004399999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2153</v>
+        <v>23.9525</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3216</v>
+        <v>8.4384</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5369</v>
+        <v>15.5143</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2961</v>
+        <v>23.1517</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5999</v>
+        <v>11.6782</v>
       </c>
       <c r="L13" t="n">
-        <v>3.6962</v>
+        <v>11.4735</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.0808</v>
+        <v>0.8008000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9215</v>
+        <v>-3.2397</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1593</v>
+        <v>4.0405</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>9.999999999987796e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-11.7206</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>11.7206</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3459</v>
+        <v>9.2578</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3063</v>
+        <v>7.292</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6522</v>
+        <v>1.9659</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5545</v>
+        <v>2.1053</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8317</v>
+        <v>8.588099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2772</v>
-      </c>
+        <v>-6.4831</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MONTSERRAT SERRA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.8904</v>
+        <v>0.0332</v>
       </c>
       <c r="E14" t="n">
-        <v>1.358</v>
+        <v>3.4806</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2484</v>
+        <v>-3.4474</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.0319</v>
+        <v>0.2153</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8872</v>
+        <v>-1.3216</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.1447</v>
+        <v>1.5369</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6394</v>
+        <v>4.2961</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7598</v>
+        <v>0.5999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.1204</v>
+        <v>3.6962</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.6712</v>
+        <v>-4.0808</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.647</v>
+        <v>-1.9215</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0243</v>
+        <v>-2.1593</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1906</v>
+        <v>-0.3459</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1326</v>
+        <v>0.3063</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.058</v>
+        <v>-0.6522</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5507</v>
+        <v>0.5545</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8279</v>
+        <v>0.8317</v>
       </c>
       <c r="X14" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>M. MONTSERRAT SERRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.0957</v>
+        <v>-1.8904</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.6625</v>
+        <v>1.358</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5668</v>
+        <v>-3.2484</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-3.0319</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3945</v>
+        <v>-0.8872</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.23</v>
+        <v>-2.1447</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5442</v>
+        <v>0.6394</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0895</v>
+        <v>0.7598</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.1204</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0803</v>
+        <v>-3.6712</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.484</v>
+        <v>-1.647</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4037</v>
+        <v>-2.0243</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0915</v>
+        <v>-1.1906</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5346</v>
+        <v>-0.1326</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4431</v>
+        <v>-1.058</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.5507</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>1.8279</v>
       </c>
       <c r="X15" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SALAVEDRA VILARNAU</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.2683</v>
+        <v>-2.0957</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0704</v>
+        <v>-2.6625</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1979</v>
+        <v>0.5668</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3461</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8619</v>
+        <v>-0.3945</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4842</v>
+        <v>-0.23</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.243</v>
+        <v>-0.5442</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.243</v>
+        <v>0.0895</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.103</v>
+        <v>-0.0803</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6188</v>
+        <v>-0.484</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4842</v>
+        <v>0.4037</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4684</v>
+        <v>0.0915</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1493</v>
+        <v>0.5346</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3191</v>
+        <v>-0.4431</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>J. SALAVEDRA VILARNAU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.656</v>
+        <v>-2.2683</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1434</v>
+        <v>-1.0704</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5126</v>
+        <v>-1.1979</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.6977</v>
+        <v>-2.3461</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1438</v>
+        <v>-0.8619</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5538999999999999</v>
+        <v>-1.4842</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2851</v>
+        <v>-0.243</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1637</v>
+        <v>-0.243</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9828</v>
+        <v>-2.103</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3075</v>
+        <v>-0.6188</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6753</v>
+        <v>-1.4842</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1184</v>
+        <v>0.4684</v>
       </c>
       <c r="T17" t="n">
-        <v>0.029</v>
+        <v>0.1493</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1474</v>
+        <v>0.3191</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.0601</v>
+        <v>-2.656</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8525</v>
+        <v>-0.1434</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2076</v>
+        <v>-2.5126</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.7877</v>
+        <v>-1.6977</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8693</v>
+        <v>-1.1438</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6569</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4239</v>
+        <v>0.2851</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5579</v>
+        <v>0.1637</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9818</v>
+        <v>0.1214</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3638</v>
+        <v>-1.9828</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6887</v>
+        <v>-1.3075</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6751</v>
+        <v>-0.6753</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
         <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4678</v>
+        <v>-1.1184</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9477</v>
+        <v>0.029</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5201</v>
+        <v>-1.1474</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
         <v>1.4959</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4959</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.469</v>
+        <v>-3.0601</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.614</v>
+        <v>-0.8525</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.855</v>
+        <v>-2.2076</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.1632</v>
+        <v>-1.7877</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5037</v>
+        <v>0.8693</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6595</v>
+        <v>-2.6569</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4361</v>
+        <v>-0.4239</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1433</v>
+        <v>1.5579</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5794</v>
+        <v>-1.9818</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7271</v>
+        <v>-1.3638</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.647</v>
+        <v>-0.6887</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0801</v>
+        <v>-0.6751</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1225</v>
+        <v>-1.4678</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4552</v>
+        <v>-0.9477</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6673</v>
+        <v>-0.5201</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>1.4959</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8279</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.2466</v>
+        <v>-4.469</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4847</v>
+        <v>-0.614</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.7618</v>
+        <v>-3.855</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.266</v>
+        <v>-3.1632</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1059</v>
+        <v>-1.5037</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3719</v>
+        <v>-1.6595</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.284</v>
+        <v>-0.4361</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0642</v>
+        <v>0.1433</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3482</v>
+        <v>-0.5794</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.982</v>
+        <v>-2.7271</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9583</v>
+        <v>-1.647</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0237</v>
+        <v>-1.0801</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.348</v>
+        <v>-1.1225</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2008</v>
+        <v>-0.4552</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1472</v>
+        <v>-0.6673</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-1.5507</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
         <v>-1.8279</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4162</v>
+        <v>-5.2466</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1486</v>
+        <v>-0.4847</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2676</v>
+        <v>-4.7618</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.1956</v>
+        <v>-3.266</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.2106</v>
+        <v>0.1059</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.985</v>
+        <v>-3.3719</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5387</v>
+        <v>-0.284</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.6335</v>
+        <v>1.0642</v>
       </c>
       <c r="L21" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.3482</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6569</v>
+        <v>-2.982</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5771</v>
+        <v>-0.9583</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0797</v>
+        <v>-2.0237</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.842</v>
+        <v>-0.348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8872</v>
+        <v>-0.2008</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9548</v>
+        <v>-0.1472</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>-1.8279</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9671</v>
+        <v>-5.4162</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.8666</v>
+        <v>-2.1486</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1004</v>
+        <v>-3.2676</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.0554</v>
+        <v>-4.1956</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-3.2106</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.965</v>
+        <v>-0.985</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5515</v>
+        <v>-1.5387</v>
       </c>
       <c r="K22" t="n">
-        <v>0.738</v>
+        <v>-1.6335</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.2896</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5038</v>
+        <v>-2.6569</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8283</v>
+        <v>-1.5771</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6755</v>
+        <v>-1.0797</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1033</v>
+        <v>-1.842</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3617</v>
+        <v>-0.8872</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7416</v>
+        <v>-0.9548</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8317</v>
+        <v>-0.9414</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8317</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,68 +2309,152 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
+        <v>-6.9671</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-4.8666</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-2.1004</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-4.0554</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.09030000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-3.965</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-3.2896</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.5038</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.8283</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.6755</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.1033</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.3617</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.7416</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.8317</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484252_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CB QUART GRUES CRUZ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>-34.0362</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>-8.004100000000001</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F24" t="n">
         <v>-26.0319</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G24" t="n">
         <v>-23.9528</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H24" t="n">
         <v>-8.4384</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I24" t="n">
         <v>-15.5142</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>-0.8008000000000002</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K24" t="n">
         <v>3.2398</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>-4.0407</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M24" t="n">
         <v>-23.1517</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N24" t="n">
         <v>-11.6782</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O24" t="n">
         <v>-11.4735</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P24" t="n">
         <v>-9.999999999998899e-05</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q24" t="n">
         <v>-11.7204</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R24" t="n">
         <v>11.7205</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S24" t="n">
         <v>-7.978599999999999</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>-1.966</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>-6.0126</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V24" t="n">
         <v>-2.1051</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W24" t="n">
         <v>6.483</v>
       </c>
-      <c r="X23" t="n">
+      <c r="X24" t="n">
         <v>-8.588099999999999</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
